--- a/Sensitivity_PSNR_Plane.xlsx
+++ b/Sensitivity_PSNR_Plane.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{821386DF-3D2F-43AA-956B-F05C02749231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39ECB0C4-519F-45C0-87E5-F44AE2CB2FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26D5692D-E885-4E5B-8F64-21ED0ABBCE00}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BCCC2881-D16C-4F7B-96DE-33539A427222}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EF09E6-71AD-4162-8221-7A6B55A3654B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18B3B62-A886-456E-89CA-30118DE6316B}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B3077C0-6C1E-481B-A1F3-0F36942D392D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DDBA0F-C54C-49D9-8715-E2133EA0033C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567D61A5-D241-4C96-8C07-225018ADF1E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07162C5-5AB1-459F-B299-0FBDA99C23DE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
